--- a/bloodmoon/블러드문_기본룰북_데이터.xlsx
+++ b/bloodmoon/블러드문_기본룰북_데이터.xlsx
@@ -11,8 +11,8 @@
     <sheet name="아이템(룰북)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'어빌리티(룰북)'!$A$1:$I$509</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'아이템(룰북)'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'어빌리티(룰북)'!$A$1:$J$581</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'아이템(룰북)'!$A$1:$G$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I509"/>
+  <dimension ref="A1:J581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.8" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="9.6" customWidth="1" min="8" max="8"/>
     <col width="19.1" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,6 +506,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>룰북</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -549,6 +555,11 @@
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -591,6 +602,11 @@
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -633,6 +649,11 @@
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -675,6 +696,11 @@
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -717,6 +743,11 @@
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -759,6 +790,11 @@
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -801,6 +837,11 @@
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -843,6 +884,11 @@
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -885,6 +931,11 @@
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -927,6 +978,11 @@
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -969,6 +1025,11 @@
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1011,6 +1072,11 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1055,6 +1121,11 @@
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1097,6 +1168,11 @@
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1139,6 +1215,11 @@
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1181,6 +1262,11 @@
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1223,6 +1309,11 @@
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1265,6 +1356,11 @@
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1309,6 +1405,11 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1351,6 +1452,11 @@
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1394,6 +1500,11 @@
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1436,6 +1547,11 @@
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1478,6 +1594,11 @@
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1520,6 +1641,11 @@
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1564,6 +1690,11 @@
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1606,6 +1737,11 @@
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1648,6 +1784,11 @@
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1690,6 +1831,11 @@
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1732,6 +1878,11 @@
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1774,6 +1925,11 @@
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1816,6 +1972,11 @@
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1858,6 +2019,11 @@
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1900,6 +2066,11 @@
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1942,6 +2113,11 @@
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1984,6 +2160,11 @@
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2026,6 +2207,11 @@
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2068,6 +2254,11 @@
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2110,6 +2301,11 @@
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2152,6 +2348,11 @@
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2194,6 +2395,11 @@
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2236,6 +2442,11 @@
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2282,6 +2493,11 @@
           <t>역) scheme</t>
         </is>
       </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2326,6 +2542,11 @@
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2371,6 +2592,11 @@
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2413,6 +2639,11 @@
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2455,6 +2686,11 @@
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2497,6 +2733,11 @@
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2539,6 +2780,11 @@
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2583,6 +2829,11 @@
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2625,6 +2876,11 @@
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2667,6 +2923,11 @@
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2709,6 +2970,11 @@
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2751,6 +3017,11 @@
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2793,6 +3064,11 @@
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2835,6 +3111,11 @@
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2877,6 +3158,11 @@
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2919,6 +3205,11 @@
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2961,6 +3252,11 @@
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3003,6 +3299,11 @@
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3049,6 +3350,11 @@
           <t>역) righteous strike</t>
         </is>
       </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3095,6 +3401,11 @@
           <t>역) 帰命帰依</t>
         </is>
       </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3137,6 +3448,11 @@
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3179,6 +3495,11 @@
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3221,6 +3542,11 @@
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3263,6 +3589,11 @@
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3305,6 +3636,11 @@
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3347,6 +3683,11 @@
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3389,6 +3730,11 @@
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3431,6 +3777,11 @@
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3473,6 +3824,11 @@
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3515,6 +3871,11 @@
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3557,6 +3918,11 @@
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3599,6 +3965,11 @@
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3641,6 +4012,11 @@
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3683,6 +4059,11 @@
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3725,6 +4106,11 @@
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3767,6 +4153,11 @@
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3809,6 +4200,11 @@
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3851,6 +4247,11 @@
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3893,6 +4294,11 @@
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3935,6 +4341,11 @@
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3977,6 +4388,11 @@
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4019,6 +4435,11 @@
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4061,6 +4482,11 @@
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4103,6 +4529,11 @@
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4145,6 +4576,11 @@
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4187,6 +4623,11 @@
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4229,6 +4670,11 @@
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4271,6 +4717,11 @@
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4313,6 +4764,11 @@
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4355,6 +4811,11 @@
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4397,6 +4858,11 @@
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4439,6 +4905,11 @@
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4481,6 +4952,11 @@
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4523,6 +4999,11 @@
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4565,6 +5046,11 @@
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4607,6 +5093,11 @@
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4649,6 +5140,11 @@
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4691,6 +5187,11 @@
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4733,6 +5234,11 @@
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4775,6 +5281,11 @@
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4817,6 +5328,11 @@
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4859,6 +5375,11 @@
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4901,6 +5422,11 @@
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4943,6 +5469,11 @@
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr"/>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4985,6 +5516,11 @@
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5027,6 +5563,11 @@
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5069,6 +5610,11 @@
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5111,6 +5657,11 @@
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5153,6 +5704,11 @@
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5195,6 +5751,11 @@
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5237,6 +5798,11 @@
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5279,6 +5845,11 @@
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5321,6 +5892,11 @@
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5363,6 +5939,11 @@
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5405,6 +5986,11 @@
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -5447,6 +6033,11 @@
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5489,6 +6080,11 @@
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5531,6 +6127,11 @@
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5573,6 +6174,11 @@
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5615,6 +6221,11 @@
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5657,6 +6268,11 @@
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5699,6 +6315,11 @@
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5741,6 +6362,11 @@
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5783,6 +6409,11 @@
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5825,6 +6456,11 @@
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5867,6 +6503,11 @@
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5909,6 +6550,11 @@
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5951,6 +6597,11 @@
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5993,6 +6644,11 @@
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6035,6 +6691,11 @@
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -6077,6 +6738,11 @@
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr"/>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -6119,6 +6785,11 @@
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -6161,6 +6832,11 @@
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6203,6 +6879,11 @@
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr"/>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6245,6 +6926,11 @@
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -6287,6 +6973,11 @@
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -6329,6 +7020,11 @@
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr"/>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -6371,6 +7067,11 @@
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr"/>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -6413,6 +7114,11 @@
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr"/>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -6455,6 +7161,11 @@
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr"/>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -6497,6 +7208,11 @@
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr"/>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -6539,6 +7255,11 @@
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr"/>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -6581,6 +7302,11 @@
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -6623,6 +7349,11 @@
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr"/>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6665,6 +7396,11 @@
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -6707,6 +7443,11 @@
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr"/>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -6749,6 +7490,11 @@
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6791,6 +7537,11 @@
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6833,6 +7584,11 @@
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr"/>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6875,6 +7631,11 @@
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6917,6 +7678,11 @@
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr"/>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6959,6 +7725,11 @@
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -7001,6 +7772,11 @@
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -7043,6 +7819,11 @@
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -7085,6 +7866,11 @@
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr"/>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -7127,6 +7913,11 @@
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr"/>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -7169,6 +7960,11 @@
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr"/>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -7211,6 +8007,11 @@
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -7253,6 +8054,11 @@
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -7295,6 +8101,11 @@
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -7337,6 +8148,11 @@
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr"/>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -7379,6 +8195,11 @@
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr"/>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -7421,6 +8242,11 @@
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr"/>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -7463,6 +8289,11 @@
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -7505,6 +8336,11 @@
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr"/>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -7547,6 +8383,11 @@
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr"/>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -7589,6 +8430,11 @@
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr"/>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -7631,6 +8477,11 @@
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -7673,6 +8524,11 @@
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr"/>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -7715,6 +8571,11 @@
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr"/>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -7757,6 +8618,11 @@
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr"/>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -7799,6 +8665,11 @@
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr"/>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -7841,6 +8712,11 @@
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr"/>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -7883,6 +8759,11 @@
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr"/>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -7925,6 +8806,11 @@
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr"/>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7967,6 +8853,11 @@
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr"/>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -8009,6 +8900,11 @@
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr"/>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -8051,6 +8947,11 @@
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr"/>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -8093,6 +8994,11 @@
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -8135,6 +9041,11 @@
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -8177,6 +9088,11 @@
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr"/>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -8219,6 +9135,11 @@
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -8261,6 +9182,11 @@
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr"/>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -8303,6 +9229,11 @@
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -8345,6 +9276,11 @@
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr"/>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -8387,6 +9323,11 @@
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr"/>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -8429,6 +9370,11 @@
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr"/>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -8471,6 +9417,11 @@
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr"/>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -8517,6 +9468,11 @@
           <t>역) 洒脫</t>
         </is>
       </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -8559,6 +9515,11 @@
         </is>
       </c>
       <c r="I192" s="4" t="inlineStr"/>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -8601,6 +9562,11 @@
         </is>
       </c>
       <c r="I193" s="4" t="inlineStr"/>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -8647,6 +9613,11 @@
           <t>역) vicarious</t>
         </is>
       </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -8689,6 +9660,11 @@
         </is>
       </c>
       <c r="I195" s="4" t="inlineStr"/>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -8731,6 +9707,11 @@
         </is>
       </c>
       <c r="I196" s="4" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -8773,6 +9754,11 @@
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr"/>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -8815,6 +9801,11 @@
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr"/>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -8857,6 +9848,11 @@
         </is>
       </c>
       <c r="I199" s="4" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -8899,6 +9895,11 @@
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr"/>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -8941,6 +9942,11 @@
         </is>
       </c>
       <c r="I201" s="4" t="inlineStr"/>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -8983,6 +9989,11 @@
         </is>
       </c>
       <c r="I202" s="4" t="inlineStr"/>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -9025,6 +10036,11 @@
         </is>
       </c>
       <c r="I203" s="4" t="inlineStr"/>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -9067,6 +10083,11 @@
         </is>
       </c>
       <c r="I204" s="4" t="inlineStr"/>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -9109,6 +10130,11 @@
         </is>
       </c>
       <c r="I205" s="4" t="inlineStr"/>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -9151,6 +10177,11 @@
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr"/>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -9193,6 +10224,11 @@
         </is>
       </c>
       <c r="I207" s="4" t="inlineStr"/>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -9235,6 +10271,11 @@
         </is>
       </c>
       <c r="I208" s="4" t="inlineStr"/>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -9277,6 +10318,11 @@
         </is>
       </c>
       <c r="I209" s="4" t="inlineStr"/>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -9319,6 +10365,11 @@
         </is>
       </c>
       <c r="I210" s="4" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -9361,6 +10412,11 @@
         </is>
       </c>
       <c r="I211" s="4" t="inlineStr"/>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -9407,6 +10463,11 @@
           <t>역) 鬼胎</t>
         </is>
       </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -9449,6 +10510,11 @@
         </is>
       </c>
       <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -9491,6 +10557,11 @@
         </is>
       </c>
       <c r="I214" s="4" t="inlineStr"/>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -9533,6 +10604,11 @@
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -9575,6 +10651,11 @@
         </is>
       </c>
       <c r="I216" s="4" t="inlineStr"/>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -9617,6 +10698,11 @@
         </is>
       </c>
       <c r="I217" s="4" t="inlineStr"/>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -9659,6 +10745,11 @@
         </is>
       </c>
       <c r="I218" s="4" t="inlineStr"/>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -9701,6 +10792,11 @@
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr"/>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -9743,6 +10839,11 @@
         </is>
       </c>
       <c r="I220" s="4" t="inlineStr"/>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -9785,6 +10886,11 @@
         </is>
       </c>
       <c r="I221" s="4" t="inlineStr"/>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -9827,6 +10933,11 @@
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr"/>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -9873,6 +10984,11 @@
           <t>역) Parthian shot</t>
         </is>
       </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -9915,6 +11031,11 @@
         </is>
       </c>
       <c r="I224" s="4" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -9957,6 +11078,11 @@
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr"/>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -9999,6 +11125,11 @@
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr"/>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -10041,6 +11172,11 @@
         </is>
       </c>
       <c r="I227" s="4" t="inlineStr"/>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -10083,6 +11219,11 @@
         </is>
       </c>
       <c r="I228" s="4" t="inlineStr"/>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -10125,6 +11266,11 @@
         </is>
       </c>
       <c r="I229" s="4" t="inlineStr"/>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -10167,6 +11313,11 @@
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr"/>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -10209,6 +11360,11 @@
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr"/>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -10251,6 +11407,11 @@
         </is>
       </c>
       <c r="I232" s="4" t="inlineStr"/>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -10293,6 +11454,11 @@
         </is>
       </c>
       <c r="I233" s="4" t="inlineStr"/>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -10335,6 +11501,11 @@
         </is>
       </c>
       <c r="I234" s="4" t="inlineStr"/>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -10377,6 +11548,11 @@
         </is>
       </c>
       <c r="I235" s="4" t="inlineStr"/>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -10419,6 +11595,11 @@
         </is>
       </c>
       <c r="I236" s="4" t="inlineStr"/>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -10461,6 +11642,11 @@
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr"/>
+      <c r="J237" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -10503,6 +11689,11 @@
         </is>
       </c>
       <c r="I238" s="4" t="inlineStr"/>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -10545,6 +11736,11 @@
         </is>
       </c>
       <c r="I239" s="4" t="inlineStr"/>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -10587,6 +11783,11 @@
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr"/>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -10633,6 +11834,11 @@
           <t>역) 裂帛</t>
         </is>
       </c>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -10675,6 +11881,11 @@
         </is>
       </c>
       <c r="I242" s="4" t="inlineStr"/>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -10717,6 +11928,11 @@
         </is>
       </c>
       <c r="I243" s="4" t="inlineStr"/>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -10759,6 +11975,11 @@
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr"/>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -10801,6 +12022,11 @@
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr"/>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -10843,6 +12069,11 @@
         </is>
       </c>
       <c r="I246" s="4" t="inlineStr"/>
+      <c r="J246" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -10885,6 +12116,11 @@
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr"/>
+      <c r="J247" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -10927,6 +12163,11 @@
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr"/>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -10969,6 +12210,11 @@
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr"/>
+      <c r="J249" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -11011,6 +12257,11 @@
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr"/>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -11053,6 +12304,11 @@
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr"/>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -11095,6 +12351,11 @@
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr"/>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -11137,6 +12398,11 @@
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr"/>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -11183,6 +12449,11 @@
           <t>역) Fléchette. 날개가 달린 소형 강철 발사체.</t>
         </is>
       </c>
+      <c r="J254" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -11225,6 +12496,11 @@
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr"/>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -11267,6 +12543,11 @@
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr"/>
+      <c r="J256" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -11309,6 +12590,11 @@
         </is>
       </c>
       <c r="I257" s="4" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -11351,6 +12637,11 @@
         </is>
       </c>
       <c r="I258" s="4" t="inlineStr"/>
+      <c r="J258" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -11393,6 +12684,11 @@
         </is>
       </c>
       <c r="I259" s="4" t="inlineStr"/>
+      <c r="J259" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -11435,6 +12731,11 @@
         </is>
       </c>
       <c r="I260" s="4" t="inlineStr"/>
+      <c r="J260" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -11477,6 +12778,11 @@
         </is>
       </c>
       <c r="I261" s="4" t="inlineStr"/>
+      <c r="J261" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -11523,6 +12829,11 @@
           <t>역) Strafe. 기관총으로 포격하다.</t>
         </is>
       </c>
+      <c r="J262" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -11565,6 +12876,11 @@
         </is>
       </c>
       <c r="I263" s="4" t="inlineStr"/>
+      <c r="J263" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -11607,6 +12923,11 @@
         </is>
       </c>
       <c r="I264" s="4" t="inlineStr"/>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -11649,6 +12970,11 @@
         </is>
       </c>
       <c r="I265" s="4" t="inlineStr"/>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -11691,6 +13017,11 @@
         </is>
       </c>
       <c r="I266" s="4" t="inlineStr"/>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -11733,6 +13064,11 @@
         </is>
       </c>
       <c r="I267" s="4" t="inlineStr"/>
+      <c r="J267" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -11775,6 +13111,11 @@
         </is>
       </c>
       <c r="I268" s="4" t="inlineStr"/>
+      <c r="J268" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -11817,6 +13158,11 @@
         </is>
       </c>
       <c r="I269" s="4" t="inlineStr"/>
+      <c r="J269" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -11859,6 +13205,11 @@
         </is>
       </c>
       <c r="I270" s="4" t="inlineStr"/>
+      <c r="J270" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -11901,6 +13252,11 @@
         </is>
       </c>
       <c r="I271" s="4" t="inlineStr"/>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -11943,6 +13299,11 @@
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr"/>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -11985,6 +13346,11 @@
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr"/>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -12027,6 +13393,11 @@
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr"/>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -12069,6 +13440,11 @@
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr"/>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -12111,6 +13487,11 @@
         </is>
       </c>
       <c r="I276" s="4" t="inlineStr"/>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -12155,6 +13536,11 @@
         </is>
       </c>
       <c r="I277" s="4" t="inlineStr"/>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -12197,6 +13583,11 @@
         </is>
       </c>
       <c r="I278" s="4" t="inlineStr"/>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -12239,6 +13630,11 @@
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr"/>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -12281,6 +13677,11 @@
         </is>
       </c>
       <c r="I280" s="4" t="inlineStr"/>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -12323,6 +13724,11 @@
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr"/>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -12365,6 +13771,11 @@
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr"/>
+      <c r="J282" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -12407,6 +13818,11 @@
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr"/>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -12449,6 +13865,11 @@
         </is>
       </c>
       <c r="I284" s="4" t="inlineStr"/>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -12491,6 +13912,11 @@
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr"/>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -12533,6 +13959,11 @@
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr"/>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -12575,6 +14006,11 @@
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr"/>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -12617,6 +14053,11 @@
         </is>
       </c>
       <c r="I288" s="4" t="inlineStr"/>
+      <c r="J288" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -12659,6 +14100,11 @@
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr"/>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -12701,6 +14147,11 @@
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr"/>
+      <c r="J290" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -12743,6 +14194,11 @@
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr"/>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -12785,6 +14241,11 @@
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr"/>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -12827,6 +14288,11 @@
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr"/>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -12869,6 +14335,11 @@
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr"/>
+      <c r="J294" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -12911,6 +14382,11 @@
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr"/>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -12953,6 +14429,11 @@
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr"/>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -12995,6 +14476,11 @@
         </is>
       </c>
       <c r="I297" s="4" t="inlineStr"/>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -13037,6 +14523,11 @@
         </is>
       </c>
       <c r="I298" s="4" t="inlineStr"/>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -13079,6 +14570,11 @@
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr"/>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -13121,6 +14617,11 @@
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr"/>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -13163,6 +14664,11 @@
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr"/>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -13205,6 +14711,11 @@
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr"/>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -13247,6 +14758,11 @@
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr"/>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -13289,6 +14805,11 @@
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr"/>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -13331,6 +14852,11 @@
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr"/>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -13373,6 +14899,11 @@
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr"/>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -13415,6 +14946,11 @@
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr"/>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -13457,6 +14993,11 @@
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr"/>
+      <c r="J308" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -13499,6 +15040,11 @@
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr"/>
+      <c r="J309" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -13541,6 +15087,11 @@
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr"/>
+      <c r="J310" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -13583,6 +15134,11 @@
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr"/>
+      <c r="J311" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -13625,6 +15181,11 @@
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr"/>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -13667,6 +15228,11 @@
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr"/>
+      <c r="J313" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -13709,6 +15275,11 @@
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr"/>
+      <c r="J314" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -13751,6 +15322,11 @@
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr"/>
+      <c r="J315" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -13793,6 +15369,11 @@
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr"/>
+      <c r="J316" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -13835,6 +15416,11 @@
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr"/>
+      <c r="J317" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -13877,6 +15463,11 @@
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr"/>
+      <c r="J318" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -13919,6 +15510,11 @@
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr"/>
+      <c r="J319" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -13961,6 +15557,11 @@
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr"/>
+      <c r="J320" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -14003,6 +15604,11 @@
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr"/>
+      <c r="J321" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -14049,6 +15655,11 @@
           <t>역) barbed wire</t>
         </is>
       </c>
+      <c r="J322" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -14091,6 +15702,11 @@
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr"/>
+      <c r="J323" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -14133,6 +15749,11 @@
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr"/>
+      <c r="J324" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -14175,6 +15796,11 @@
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr"/>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -14219,6 +15845,11 @@
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr"/>
+      <c r="J326" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -14263,6 +15894,11 @@
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr"/>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -14307,6 +15943,11 @@
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr"/>
+      <c r="J328" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -14351,6 +15992,11 @@
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr"/>
+      <c r="J329" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -14395,6 +16041,11 @@
         </is>
       </c>
       <c r="I330" s="4" t="inlineStr"/>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -14439,6 +16090,11 @@
         </is>
       </c>
       <c r="I331" s="4" t="inlineStr"/>
+      <c r="J331" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -14483,6 +16139,11 @@
         </is>
       </c>
       <c r="I332" s="4" t="inlineStr"/>
+      <c r="J332" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -14527,6 +16188,11 @@
         </is>
       </c>
       <c r="I333" s="4" t="inlineStr"/>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -14571,6 +16237,11 @@
         </is>
       </c>
       <c r="I334" s="4" t="inlineStr"/>
+      <c r="J334" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -14615,6 +16286,11 @@
         </is>
       </c>
       <c r="I335" s="4" t="inlineStr"/>
+      <c r="J335" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -14659,6 +16335,11 @@
         </is>
       </c>
       <c r="I336" s="4" t="inlineStr"/>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -14703,6 +16384,11 @@
         </is>
       </c>
       <c r="I337" s="4" t="inlineStr"/>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -14747,6 +16433,11 @@
         </is>
       </c>
       <c r="I338" s="4" t="inlineStr"/>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -14791,6 +16482,11 @@
         </is>
       </c>
       <c r="I339" s="4" t="inlineStr"/>
+      <c r="J339" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -14833,6 +16529,11 @@
         </is>
       </c>
       <c r="I340" s="4" t="inlineStr"/>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -14877,6 +16578,11 @@
         </is>
       </c>
       <c r="I341" s="4" t="inlineStr"/>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -14919,6 +16625,11 @@
         </is>
       </c>
       <c r="I342" s="4" t="inlineStr"/>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -14961,6 +16672,11 @@
         </is>
       </c>
       <c r="I343" s="4" t="inlineStr"/>
+      <c r="J343" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -15003,6 +16719,11 @@
         </is>
       </c>
       <c r="I344" s="4" t="inlineStr"/>
+      <c r="J344" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -15045,6 +16766,11 @@
         </is>
       </c>
       <c r="I345" s="4" t="inlineStr"/>
+      <c r="J345" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -15087,6 +16813,11 @@
         </is>
       </c>
       <c r="I346" s="4" t="inlineStr"/>
+      <c r="J346" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -15129,6 +16860,11 @@
         </is>
       </c>
       <c r="I347" s="4" t="inlineStr"/>
+      <c r="J347" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -15173,6 +16909,11 @@
         </is>
       </c>
       <c r="I348" s="4" t="inlineStr"/>
+      <c r="J348" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -15215,6 +16956,11 @@
         </is>
       </c>
       <c r="I349" s="4" t="inlineStr"/>
+      <c r="J349" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -15257,6 +17003,11 @@
         </is>
       </c>
       <c r="I350" s="4" t="inlineStr"/>
+      <c r="J350" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -15299,6 +17050,11 @@
         </is>
       </c>
       <c r="I351" s="4" t="inlineStr"/>
+      <c r="J351" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -15341,6 +17097,11 @@
         </is>
       </c>
       <c r="I352" s="4" t="inlineStr"/>
+      <c r="J352" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -15385,6 +17146,11 @@
         </is>
       </c>
       <c r="I353" s="4" t="inlineStr"/>
+      <c r="J353" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -15427,6 +17193,11 @@
         </is>
       </c>
       <c r="I354" s="4" t="inlineStr"/>
+      <c r="J354" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -15471,6 +17242,11 @@
         </is>
       </c>
       <c r="I355" s="4" t="inlineStr"/>
+      <c r="J355" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -15513,6 +17289,11 @@
         </is>
       </c>
       <c r="I356" s="4" t="inlineStr"/>
+      <c r="J356" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -15555,6 +17336,11 @@
         </is>
       </c>
       <c r="I357" s="4" t="inlineStr"/>
+      <c r="J357" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -15597,6 +17383,11 @@
         </is>
       </c>
       <c r="I358" s="4" t="inlineStr"/>
+      <c r="J358" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -15639,6 +17430,11 @@
         </is>
       </c>
       <c r="I359" s="4" t="inlineStr"/>
+      <c r="J359" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -15681,6 +17477,11 @@
         </is>
       </c>
       <c r="I360" s="4" t="inlineStr"/>
+      <c r="J360" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -15723,6 +17524,11 @@
         </is>
       </c>
       <c r="I361" s="4" t="inlineStr"/>
+      <c r="J361" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -15765,6 +17571,11 @@
         </is>
       </c>
       <c r="I362" s="4" t="inlineStr"/>
+      <c r="J362" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -15807,6 +17618,11 @@
         </is>
       </c>
       <c r="I363" s="4" t="inlineStr"/>
+      <c r="J363" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -15853,6 +17669,11 @@
           <t>역) 瘴気</t>
         </is>
       </c>
+      <c r="J364" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -15895,6 +17716,11 @@
         </is>
       </c>
       <c r="I365" s="4" t="inlineStr"/>
+      <c r="J365" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -15937,6 +17763,11 @@
         </is>
       </c>
       <c r="I366" s="4" t="inlineStr"/>
+      <c r="J366" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -15979,6 +17810,11 @@
         </is>
       </c>
       <c r="I367" s="4" t="inlineStr"/>
+      <c r="J367" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -16021,6 +17857,11 @@
         </is>
       </c>
       <c r="I368" s="4" t="inlineStr"/>
+      <c r="J368" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -16063,6 +17904,11 @@
         </is>
       </c>
       <c r="I369" s="4" t="inlineStr"/>
+      <c r="J369" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -16109,6 +17955,11 @@
           <t>역) Lubricator</t>
         </is>
       </c>
+      <c r="J370" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -16151,6 +18002,11 @@
         </is>
       </c>
       <c r="I371" s="4" t="inlineStr"/>
+      <c r="J371" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -16193,6 +18049,11 @@
         </is>
       </c>
       <c r="I372" s="4" t="inlineStr"/>
+      <c r="J372" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -16235,6 +18096,11 @@
         </is>
       </c>
       <c r="I373" s="4" t="inlineStr"/>
+      <c r="J373" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -16277,6 +18143,11 @@
         </is>
       </c>
       <c r="I374" s="4" t="inlineStr"/>
+      <c r="J374" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -16319,6 +18190,11 @@
         </is>
       </c>
       <c r="I375" s="4" t="inlineStr"/>
+      <c r="J375" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -16361,6 +18237,11 @@
         </is>
       </c>
       <c r="I376" s="4" t="inlineStr"/>
+      <c r="J376" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -16403,6 +18284,11 @@
         </is>
       </c>
       <c r="I377" s="4" t="inlineStr"/>
+      <c r="J377" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -16445,6 +18331,11 @@
         </is>
       </c>
       <c r="I378" s="4" t="inlineStr"/>
+      <c r="J378" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -16487,6 +18378,11 @@
         </is>
       </c>
       <c r="I379" s="4" t="inlineStr"/>
+      <c r="J379" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -16529,6 +18425,11 @@
         </is>
       </c>
       <c r="I380" s="4" t="inlineStr"/>
+      <c r="J380" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -16571,6 +18472,11 @@
         </is>
       </c>
       <c r="I381" s="4" t="inlineStr"/>
+      <c r="J381" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -16613,6 +18519,11 @@
         </is>
       </c>
       <c r="I382" s="4" t="inlineStr"/>
+      <c r="J382" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -16655,6 +18566,11 @@
         </is>
       </c>
       <c r="I383" s="4" t="inlineStr"/>
+      <c r="J383" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -16697,6 +18613,11 @@
         </is>
       </c>
       <c r="I384" s="4" t="inlineStr"/>
+      <c r="J384" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -16739,6 +18660,11 @@
         </is>
       </c>
       <c r="I385" s="4" t="inlineStr"/>
+      <c r="J385" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -16781,6 +18707,11 @@
         </is>
       </c>
       <c r="I386" s="4" t="inlineStr"/>
+      <c r="J386" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -16823,6 +18754,11 @@
         </is>
       </c>
       <c r="I387" s="4" t="inlineStr"/>
+      <c r="J387" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -16865,6 +18801,11 @@
         </is>
       </c>
       <c r="I388" s="4" t="inlineStr"/>
+      <c r="J388" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -16907,6 +18848,11 @@
         </is>
       </c>
       <c r="I389" s="4" t="inlineStr"/>
+      <c r="J389" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -16949,6 +18895,11 @@
         </is>
       </c>
       <c r="I390" s="4" t="inlineStr"/>
+      <c r="J390" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -16991,6 +18942,11 @@
         </is>
       </c>
       <c r="I391" s="4" t="inlineStr"/>
+      <c r="J391" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -17033,6 +18989,11 @@
         </is>
       </c>
       <c r="I392" s="4" t="inlineStr"/>
+      <c r="J392" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -17075,6 +19036,11 @@
         </is>
       </c>
       <c r="I393" s="4" t="inlineStr"/>
+      <c r="J393" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -17117,6 +19083,11 @@
         </is>
       </c>
       <c r="I394" s="4" t="inlineStr"/>
+      <c r="J394" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -17159,6 +19130,11 @@
         </is>
       </c>
       <c r="I395" s="4" t="inlineStr"/>
+      <c r="J395" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -17201,6 +19177,11 @@
         </is>
       </c>
       <c r="I396" s="4" t="inlineStr"/>
+      <c r="J396" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -17243,6 +19224,11 @@
         </is>
       </c>
       <c r="I397" s="4" t="inlineStr"/>
+      <c r="J397" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -17285,6 +19271,11 @@
         </is>
       </c>
       <c r="I398" s="4" t="inlineStr"/>
+      <c r="J398" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -17327,6 +19318,11 @@
         </is>
       </c>
       <c r="I399" s="4" t="inlineStr"/>
+      <c r="J399" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -17369,6 +19365,11 @@
         </is>
       </c>
       <c r="I400" s="4" t="inlineStr"/>
+      <c r="J400" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -17411,6 +19412,11 @@
         </is>
       </c>
       <c r="I401" s="4" t="inlineStr"/>
+      <c r="J401" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -17453,6 +19459,11 @@
         </is>
       </c>
       <c r="I402" s="4" t="inlineStr"/>
+      <c r="J402" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -17495,6 +19506,11 @@
         </is>
       </c>
       <c r="I403" s="4" t="inlineStr"/>
+      <c r="J403" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -17537,6 +19553,11 @@
         </is>
       </c>
       <c r="I404" s="4" t="inlineStr"/>
+      <c r="J404" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -17579,6 +19600,11 @@
         </is>
       </c>
       <c r="I405" s="4" t="inlineStr"/>
+      <c r="J405" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -17621,6 +19647,11 @@
         </is>
       </c>
       <c r="I406" s="4" t="inlineStr"/>
+      <c r="J406" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -17663,6 +19694,11 @@
         </is>
       </c>
       <c r="I407" s="4" t="inlineStr"/>
+      <c r="J407" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -17705,6 +19741,11 @@
         </is>
       </c>
       <c r="I408" s="4" t="inlineStr"/>
+      <c r="J408" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -17747,6 +19788,11 @@
         </is>
       </c>
       <c r="I409" s="4" t="inlineStr"/>
+      <c r="J409" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -17789,6 +19835,11 @@
         </is>
       </c>
       <c r="I410" s="4" t="inlineStr"/>
+      <c r="J410" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -17831,6 +19882,11 @@
         </is>
       </c>
       <c r="I411" s="4" t="inlineStr"/>
+      <c r="J411" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -17873,6 +19929,11 @@
         </is>
       </c>
       <c r="I412" s="4" t="inlineStr"/>
+      <c r="J412" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -17915,6 +19976,11 @@
         </is>
       </c>
       <c r="I413" s="4" t="inlineStr"/>
+      <c r="J413" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -17957,6 +20023,11 @@
         </is>
       </c>
       <c r="I414" s="4" t="inlineStr"/>
+      <c r="J414" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -17999,6 +20070,11 @@
         </is>
       </c>
       <c r="I415" s="4" t="inlineStr"/>
+      <c r="J415" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -18041,6 +20117,11 @@
         </is>
       </c>
       <c r="I416" s="4" t="inlineStr"/>
+      <c r="J416" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -18087,6 +20168,11 @@
           <t>역) 赤化</t>
         </is>
       </c>
+      <c r="J417" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -18129,6 +20215,11 @@
         </is>
       </c>
       <c r="I418" s="4" t="inlineStr"/>
+      <c r="J418" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -18171,6 +20262,11 @@
         </is>
       </c>
       <c r="I419" s="4" t="inlineStr"/>
+      <c r="J419" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -18213,6 +20309,11 @@
         </is>
       </c>
       <c r="I420" s="4" t="inlineStr"/>
+      <c r="J420" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -18255,6 +20356,11 @@
         </is>
       </c>
       <c r="I421" s="4" t="inlineStr"/>
+      <c r="J421" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -18297,6 +20403,11 @@
         </is>
       </c>
       <c r="I422" s="4" t="inlineStr"/>
+      <c r="J422" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -18339,6 +20450,11 @@
         </is>
       </c>
       <c r="I423" s="4" t="inlineStr"/>
+      <c r="J423" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -18381,6 +20497,11 @@
         </is>
       </c>
       <c r="I424" s="4" t="inlineStr"/>
+      <c r="J424" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -18423,6 +20544,11 @@
         </is>
       </c>
       <c r="I425" s="4" t="inlineStr"/>
+      <c r="J425" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -18465,6 +20591,11 @@
         </is>
       </c>
       <c r="I426" s="4" t="inlineStr"/>
+      <c r="J426" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -18507,6 +20638,11 @@
         </is>
       </c>
       <c r="I427" s="4" t="inlineStr"/>
+      <c r="J427" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -18549,6 +20685,11 @@
         </is>
       </c>
       <c r="I428" s="4" t="inlineStr"/>
+      <c r="J428" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -18591,6 +20732,11 @@
         </is>
       </c>
       <c r="I429" s="4" t="inlineStr"/>
+      <c r="J429" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -18635,6 +20781,11 @@
         </is>
       </c>
       <c r="I430" s="4" t="inlineStr"/>
+      <c r="J430" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -18679,6 +20830,11 @@
         </is>
       </c>
       <c r="I431" s="4" t="inlineStr"/>
+      <c r="J431" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -18721,6 +20877,11 @@
         </is>
       </c>
       <c r="I432" s="4" t="inlineStr"/>
+      <c r="J432" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -18765,6 +20926,11 @@
         </is>
       </c>
       <c r="I433" s="4" t="inlineStr"/>
+      <c r="J433" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -18809,6 +20975,11 @@
         </is>
       </c>
       <c r="I434" s="4" t="inlineStr"/>
+      <c r="J434" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -18851,6 +21022,11 @@
         </is>
       </c>
       <c r="I435" s="4" t="inlineStr"/>
+      <c r="J435" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -18893,6 +21069,11 @@
         </is>
       </c>
       <c r="I436" s="4" t="inlineStr"/>
+      <c r="J436" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -18935,6 +21116,11 @@
         </is>
       </c>
       <c r="I437" s="4" t="inlineStr"/>
+      <c r="J437" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -18977,6 +21163,11 @@
         </is>
       </c>
       <c r="I438" s="4" t="inlineStr"/>
+      <c r="J438" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -19019,6 +21210,11 @@
         </is>
       </c>
       <c r="I439" s="4" t="inlineStr"/>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -19061,6 +21257,11 @@
         </is>
       </c>
       <c r="I440" s="4" t="inlineStr"/>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -19103,6 +21304,11 @@
         </is>
       </c>
       <c r="I441" s="4" t="inlineStr"/>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -19149,6 +21355,11 @@
           <t>역) Field Prep</t>
         </is>
       </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -19191,6 +21402,11 @@
         </is>
       </c>
       <c r="I443" s="4" t="inlineStr"/>
+      <c r="J443" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -19233,6 +21449,11 @@
         </is>
       </c>
       <c r="I444" s="4" t="inlineStr"/>
+      <c r="J444" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -19275,6 +21496,11 @@
         </is>
       </c>
       <c r="I445" s="4" t="inlineStr"/>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -19317,6 +21543,11 @@
         </is>
       </c>
       <c r="I446" s="4" t="inlineStr"/>
+      <c r="J446" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -19359,6 +21590,11 @@
         </is>
       </c>
       <c r="I447" s="4" t="inlineStr"/>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -19401,6 +21637,11 @@
         </is>
       </c>
       <c r="I448" s="4" t="inlineStr"/>
+      <c r="J448" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -19445,6 +21686,11 @@
         </is>
       </c>
       <c r="I449" s="4" t="inlineStr"/>
+      <c r="J449" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -19487,6 +21733,11 @@
         </is>
       </c>
       <c r="I450" s="4" t="inlineStr"/>
+      <c r="J450" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -19533,6 +21784,11 @@
           <t>역) agony</t>
         </is>
       </c>
+      <c r="J451" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -19575,6 +21831,11 @@
         </is>
       </c>
       <c r="I452" s="4" t="inlineStr"/>
+      <c r="J452" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -19617,6 +21878,11 @@
         </is>
       </c>
       <c r="I453" s="4" t="inlineStr"/>
+      <c r="J453" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -19659,6 +21925,11 @@
         </is>
       </c>
       <c r="I454" s="4" t="inlineStr"/>
+      <c r="J454" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -19701,6 +21972,11 @@
         </is>
       </c>
       <c r="I455" s="4" t="inlineStr"/>
+      <c r="J455" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -19743,6 +22019,11 @@
         </is>
       </c>
       <c r="I456" s="4" t="inlineStr"/>
+      <c r="J456" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -19785,6 +22066,11 @@
         </is>
       </c>
       <c r="I457" s="4" t="inlineStr"/>
+      <c r="J457" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -19827,6 +22113,11 @@
         </is>
       </c>
       <c r="I458" s="4" t="inlineStr"/>
+      <c r="J458" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -19869,6 +22160,11 @@
         </is>
       </c>
       <c r="I459" s="4" t="inlineStr"/>
+      <c r="J459" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -19911,6 +22207,11 @@
         </is>
       </c>
       <c r="I460" s="4" t="inlineStr"/>
+      <c r="J460" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -19953,6 +22254,11 @@
         </is>
       </c>
       <c r="I461" s="4" t="inlineStr"/>
+      <c r="J461" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -19995,6 +22301,11 @@
         </is>
       </c>
       <c r="I462" s="4" t="inlineStr"/>
+      <c r="J462" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -20037,6 +22348,11 @@
         </is>
       </c>
       <c r="I463" s="4" t="inlineStr"/>
+      <c r="J463" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -20079,6 +22395,11 @@
         </is>
       </c>
       <c r="I464" s="4" t="inlineStr"/>
+      <c r="J464" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -20121,6 +22442,11 @@
         </is>
       </c>
       <c r="I465" s="4" t="inlineStr"/>
+      <c r="J465" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -20163,6 +22489,11 @@
         </is>
       </c>
       <c r="I466" s="4" t="inlineStr"/>
+      <c r="J466" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -20205,6 +22536,11 @@
         </is>
       </c>
       <c r="I467" s="4" t="inlineStr"/>
+      <c r="J467" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -20247,6 +22583,11 @@
         </is>
       </c>
       <c r="I468" s="4" t="inlineStr"/>
+      <c r="J468" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -20289,6 +22630,11 @@
         </is>
       </c>
       <c r="I469" s="4" t="inlineStr"/>
+      <c r="J469" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -20331,6 +22677,11 @@
         </is>
       </c>
       <c r="I470" s="4" t="inlineStr"/>
+      <c r="J470" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -20373,6 +22724,11 @@
         </is>
       </c>
       <c r="I471" s="4" t="inlineStr"/>
+      <c r="J471" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -20415,6 +22771,11 @@
         </is>
       </c>
       <c r="I472" s="4" t="inlineStr"/>
+      <c r="J472" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -20457,6 +22818,11 @@
         </is>
       </c>
       <c r="I473" s="4" t="inlineStr"/>
+      <c r="J473" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -20499,6 +22865,11 @@
         </is>
       </c>
       <c r="I474" s="4" t="inlineStr"/>
+      <c r="J474" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -20541,6 +22912,11 @@
         </is>
       </c>
       <c r="I475" s="4" t="inlineStr"/>
+      <c r="J475" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -20583,6 +22959,11 @@
         </is>
       </c>
       <c r="I476" s="4" t="inlineStr"/>
+      <c r="J476" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -20625,6 +23006,11 @@
         </is>
       </c>
       <c r="I477" s="4" t="inlineStr"/>
+      <c r="J477" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -20667,6 +23053,11 @@
         </is>
       </c>
       <c r="I478" s="4" t="inlineStr"/>
+      <c r="J478" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -20709,6 +23100,11 @@
         </is>
       </c>
       <c r="I479" s="4" t="inlineStr"/>
+      <c r="J479" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -20751,6 +23147,11 @@
         </is>
       </c>
       <c r="I480" s="4" t="inlineStr"/>
+      <c r="J480" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -20793,6 +23194,11 @@
         </is>
       </c>
       <c r="I481" s="4" t="inlineStr"/>
+      <c r="J481" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -20835,6 +23241,11 @@
         </is>
       </c>
       <c r="I482" s="4" t="inlineStr"/>
+      <c r="J482" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -20877,6 +23288,11 @@
         </is>
       </c>
       <c r="I483" s="4" t="inlineStr"/>
+      <c r="J483" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -20919,6 +23335,11 @@
         </is>
       </c>
       <c r="I484" s="4" t="inlineStr"/>
+      <c r="J484" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -20961,6 +23382,11 @@
         </is>
       </c>
       <c r="I485" s="4" t="inlineStr"/>
+      <c r="J485" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -21003,6 +23429,11 @@
         </is>
       </c>
       <c r="I486" s="4" t="inlineStr"/>
+      <c r="J486" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -21045,6 +23476,11 @@
         </is>
       </c>
       <c r="I487" s="4" t="inlineStr"/>
+      <c r="J487" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -21087,6 +23523,11 @@
         </is>
       </c>
       <c r="I488" s="4" t="inlineStr"/>
+      <c r="J488" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -21129,6 +23570,11 @@
         </is>
       </c>
       <c r="I489" s="4" t="inlineStr"/>
+      <c r="J489" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -21171,6 +23617,11 @@
         </is>
       </c>
       <c r="I490" s="4" t="inlineStr"/>
+      <c r="J490" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -21213,6 +23664,11 @@
         </is>
       </c>
       <c r="I491" s="4" t="inlineStr"/>
+      <c r="J491" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -21255,6 +23711,11 @@
         </is>
       </c>
       <c r="I492" s="4" t="inlineStr"/>
+      <c r="J492" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -21297,6 +23758,11 @@
         </is>
       </c>
       <c r="I493" s="4" t="inlineStr"/>
+      <c r="J493" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -21339,6 +23805,11 @@
         </is>
       </c>
       <c r="I494" s="4" t="inlineStr"/>
+      <c r="J494" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -21381,6 +23852,11 @@
         </is>
       </c>
       <c r="I495" s="4" t="inlineStr"/>
+      <c r="J495" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -21423,6 +23899,11 @@
         </is>
       </c>
       <c r="I496" s="4" t="inlineStr"/>
+      <c r="J496" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -21465,6 +23946,11 @@
         </is>
       </c>
       <c r="I497" s="4" t="inlineStr"/>
+      <c r="J497" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -21507,6 +23993,11 @@
         </is>
       </c>
       <c r="I498" s="4" t="inlineStr"/>
+      <c r="J498" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -21549,6 +24040,11 @@
         </is>
       </c>
       <c r="I499" s="4" t="inlineStr"/>
+      <c r="J499" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -21591,6 +24087,11 @@
         </is>
       </c>
       <c r="I500" s="4" t="inlineStr"/>
+      <c r="J500" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -21633,6 +24134,11 @@
         </is>
       </c>
       <c r="I501" s="4" t="inlineStr"/>
+      <c r="J501" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -21675,6 +24181,11 @@
         </is>
       </c>
       <c r="I502" s="4" t="inlineStr"/>
+      <c r="J502" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -21717,6 +24228,11 @@
         </is>
       </c>
       <c r="I503" s="4" t="inlineStr"/>
+      <c r="J503" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -21759,6 +24275,11 @@
         </is>
       </c>
       <c r="I504" s="4" t="inlineStr"/>
+      <c r="J504" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -21801,6 +24322,11 @@
         </is>
       </c>
       <c r="I505" s="4" t="inlineStr"/>
+      <c r="J505" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -21843,6 +24369,11 @@
         </is>
       </c>
       <c r="I506" s="4" t="inlineStr"/>
+      <c r="J506" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -21885,6 +24416,11 @@
         </is>
       </c>
       <c r="I507" s="4" t="inlineStr"/>
+      <c r="J507" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -21927,6 +24463,11 @@
         </is>
       </c>
       <c r="I508" s="4" t="inlineStr"/>
+      <c r="J508" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -21969,9 +24510,3052 @@
         </is>
       </c>
       <c r="I509" s="4" t="inlineStr"/>
+      <c r="J509" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>소녀의 일격</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>종족:마법소녀</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>자유</t>
+        </is>
+      </c>
+      <c r="F510" s="4" t="inlineStr">
+        <is>
+          <t>공격목표에게 1d6의 대미지를 입힌다 대미지 적용 후 목표의 【여유】가 2 감소한다.</t>
+        </is>
+      </c>
+      <c r="G510" s="4" t="inlineStr"/>
+      <c r="H510" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I510" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 종족 어빌리티</t>
+        </is>
+      </c>
+      <c r="J510" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>마법소녀형태</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>종족:마법소녀</t>
+        </is>
+      </c>
+      <c r="C511" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D511" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E511" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F511" s="4" t="inlineStr">
+        <is>
+          <t>결전 페이즈의 라운드 개시 시에 사용 가능. 원하는 특기 2개를 미습득의 상태로 하고 사용불능이 되지 않은 새로운 특기를 습득할 수 있다. 이 어빌리티는 세션 중 1번만 사용 가능하다.</t>
+        </is>
+      </c>
+      <c r="G511" s="4" t="inlineStr"/>
+      <c r="H511" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I511" s="4" t="inlineStr"/>
+      <c r="J511" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>신기한 파티</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>종족:마법소녀</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D512" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E512" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F512" s="4" t="inlineStr">
+        <is>
+          <t>누군가 방어판정의 주사위를 굴리기 직전에 사용 가능하다. 그 판정에 마이너스 【자신의 레벨의 반(올림)+3】의 수정을 붙인다. 이 어빌리티는 세션 중 한 번만 사용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G512" s="4" t="inlineStr"/>
+      <c r="H512" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I512" s="4" t="inlineStr"/>
+      <c r="J512" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>기적의 일격</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>종족:마법소녀</t>
+        </is>
+      </c>
+      <c r="C513" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D513" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E513" s="3" t="inlineStr">
+        <is>
+          <t>휘두르기</t>
+        </is>
+      </c>
+      <c r="F513" s="4" t="inlineStr">
+        <is>
+          <t>팔로워 전원을 대상으로 지원판정을 행한다. 지원판정에 성공하면 목표에 대해 설득을 시도할 때, 【내구력】이 4점 낮은 것으로 친다.</t>
+        </is>
+      </c>
+      <c r="G513" s="4" t="inlineStr"/>
+      <c r="H513" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I513" s="4" t="inlineStr"/>
+      <c r="J513" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>비밀의 마법</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>종족:마법소녀</t>
+        </is>
+      </c>
+      <c r="C514" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D514" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E514" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F514" s="4" t="inlineStr">
+        <is>
+          <t>누군가(자신 포함)의 【배덕】이 파괴당하면, 자신이 공격에 의해 가하는 대미지가 2점 증가한다.</t>
+        </is>
+      </c>
+      <c r="G514" s="4" t="inlineStr"/>
+      <c r="H514" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I514" s="4" t="inlineStr"/>
+      <c r="J514" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>작은 마법</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>종족:마법소녀</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D515" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F515" s="4" t="inlineStr">
+        <is>
+          <t>전투 중 몬스터나 팔로워가 펌블했을 때, 추가행동을 한 번 습득한다. 이 추가행동으로는 타입이 【지원】인 어빌리티만 사용할 수 있다</t>
+        </is>
+      </c>
+      <c r="G515" s="4" t="inlineStr"/>
+      <c r="H515" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I515" s="4" t="inlineStr"/>
+      <c r="J515" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>우리들은 최강</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>조직:사립심연여학교</t>
+        </is>
+      </c>
+      <c r="C516" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D516" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E516" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F516" s="4" t="inlineStr">
+        <is>
+          <t>자신이 연계한 공격에 대해 방어 판정이 행해질 때, 그 판정에 마이너스 1의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G516" s="4" t="inlineStr"/>
+      <c r="H516" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I516" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 조직 어빌리티</t>
+        </is>
+      </c>
+      <c r="J516" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>운명의 선물</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>조직:사립심연여학교</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D517" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F517" s="4" t="inlineStr">
+        <is>
+          <t>자신이 교류판정을 할 때 조합하여 사용. 교류판정에 성공한 경우 자신과 교류의 목표는 서로 아이템을 하나 교환한다. 이 세션 동안 그 아이템의 소유주는 그 아이템을 파괴하면 받은 대미지를 1D6 줄이거나 주는 대미지를 1D6 상승시킬 수 있다.</t>
+        </is>
+      </c>
+      <c r="G517" s="4" t="inlineStr"/>
+      <c r="H517" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I517" s="4" t="inlineStr"/>
+      <c r="J517" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>소원의 입맞춤</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>조직:사립심연여학교</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D518" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E518" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F518" s="4" t="inlineStr">
+        <is>
+          <t>자신이 교류판정을 할 때 조합하여 사용. 교류판정에 성공한 경우 교류의 목표의 원하는 신체부위를 하나 선택한다. 그 세션 중, 그 부위는 두 번 대미지를 받지 않으면 파괴되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G518" s="4" t="inlineStr"/>
+      <c r="H518" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I518" s="4" t="inlineStr"/>
+      <c r="J518" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>빛나는 두 사람</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>조직:사립심연여학교</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D519" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E519" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F519" s="4" t="inlineStr">
+        <is>
+          <t>자신이 교류판정을 할 때 조합하여 사용. 교류판정에 성공한 경우 그 씬에 등장하고 있는 캐릭터 중 고르고 싶은 만큼 대상을 고른다. 고른 캐릭터의 【여유】를 2점 상승시킨다. 또한, 이 씬 다음의 씬에 몬스터가 행동한 경우, 그 판정에 마이너스 1의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G519" s="4" t="inlineStr"/>
+      <c r="H519" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I519" s="4" t="inlineStr"/>
+      <c r="J519" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>내가 당신의 팔이 되겠어</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>조직:사립심연여학교</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D520" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E520" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F520" s="4" t="inlineStr">
+        <is>
+          <t>자신이 관계를 가지고 있는 캐릭터를 한 명 목표로 삼는다. 지원판정에 성공하면, 목표는 사용 불가가 된 특기를 그 【심도】의 수치까지 원하는 만큼 고른다. 이 때, 자신(어빌리티 사용자)이 이미 사용불능이 된 특기는 고를 수 없다. 이 전투 동안 자신은 고른 특기가 사용불능이 되며 목표는 그 특기를 사용할 수 있게 된다.</t>
+        </is>
+      </c>
+      <c r="G520" s="4" t="inlineStr"/>
+      <c r="H520" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I520" s="4" t="inlineStr"/>
+      <c r="J520" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>순결기사의 증표</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="inlineStr">
+        <is>
+          <t>조직:사립심연여학교</t>
+        </is>
+      </c>
+      <c r="C521" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D521" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E521" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F521" s="4" t="inlineStr">
+        <is>
+          <t>이 세션 동안 자신이 받고 있는 부위 대미지의 수만큼 【타격력】이 상승한다. 그리고 이 세션 동안 자신이 부여한 부위 대미지의 수 만큼 【타격력】이 상승한다.</t>
+        </is>
+      </c>
+      <c r="G521" s="4" t="inlineStr"/>
+      <c r="H521" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I521" s="4" t="inlineStr"/>
+      <c r="J521" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>이 것은 그 사람 몫의 공격</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>조직:생츄어리</t>
+        </is>
+      </c>
+      <c r="C522" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D522" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E522" s="3" t="inlineStr">
+        <is>
+          <t>자유</t>
+        </is>
+      </c>
+      <c r="F522" s="4" t="inlineStr">
+        <is>
+          <t>공격 목표에게 【1D6+파괴된 자신의 【행복】의 수(【배덕】 포함)】의 대미지를 입힌다.</t>
+        </is>
+      </c>
+      <c r="G522" s="4" t="inlineStr"/>
+      <c r="H522" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I522" s="4" t="inlineStr"/>
+      <c r="J522" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>소중했던 사람</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>조직:생츄어리</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D523" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E523" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F523" s="4" t="inlineStr">
+        <is>
+          <t>휴식 판정에 조합하여 사용. 휴식 판정에 성공하면, 【여유】가 5점 더 상승한다.</t>
+        </is>
+      </c>
+      <c r="G523" s="4" t="inlineStr"/>
+      <c r="H523" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I523" s="4" t="inlineStr"/>
+      <c r="J523" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>에이프런</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>조직:생츄어리</t>
+        </is>
+      </c>
+      <c r="C524" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D524" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E524" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F524" s="4" t="inlineStr">
+        <is>
+          <t>자신이 파괴의 목표가 되었을 경우, 그 파괴판정에 마이너스 1의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G524" s="4" t="inlineStr"/>
+      <c r="H524" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I524" s="4" t="inlineStr"/>
+      <c r="J524" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>차가운 접시</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>조직:생츄어리</t>
+        </is>
+      </c>
+      <c r="C525" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D525" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E525" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F525" s="4" t="inlineStr">
+        <is>
+          <t>결과 페이즈의 【경험치의 획득】의 타이밍에 경험치를 1점 획득한다.</t>
+        </is>
+      </c>
+      <c r="G525" s="4" t="inlineStr"/>
+      <c r="H525" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I525" s="4" t="inlineStr"/>
+      <c r="J525" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>샘플</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>조직:생츄어리</t>
+        </is>
+      </c>
+      <c r="C526" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D526" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E526" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F526" s="4" t="inlineStr">
+        <is>
+          <t>세션 개시시에 【흥분제】나 【진정제】나 【의료키트】 중 하나를 획득한다.</t>
+        </is>
+      </c>
+      <c r="G526" s="4" t="inlineStr"/>
+      <c r="H526" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I526" s="4" t="inlineStr"/>
+      <c r="J526" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>이 이상은 더는</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>조직:생츄어리</t>
+        </is>
+      </c>
+      <c r="C527" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D527" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E527" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F527" s="4" t="inlineStr">
+        <is>
+          <t>누군가 습격에 의해 【여유】나 【혈량】이 감소했을 때, 그 감소의 일부를 대신 받을 수 있다. 몇 점을 대신 받을 지는 이 어빌리티의 사용자가 정할 수 있다. 단, 자신의 【여유】나 【혈량】이 마이너스가 되도록은 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G527" s="4" t="inlineStr"/>
+      <c r="H527" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I527" s="4" t="inlineStr"/>
+      <c r="J527" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>도약공격</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>조직:미려파</t>
+        </is>
+      </c>
+      <c r="C528" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D528" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E528" s="3" t="inlineStr">
+        <is>
+          <t>뛰기</t>
+        </is>
+      </c>
+      <c r="F528" s="4" t="inlineStr">
+        <is>
+          <t>공격 목표에게 3D6의 대미지를 입힌다. 이 공격에 대해 방어판정을 행할 경우, 마이너스 2의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G528" s="4" t="inlineStr"/>
+      <c r="H528" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I528" s="4" t="inlineStr"/>
+      <c r="J528" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>멋진 포즈</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>조직:미려파</t>
+        </is>
+      </c>
+      <c r="C529" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D529" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E529" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F529" s="4" t="inlineStr">
+        <is>
+          <t>공격에 조합하여 사용한다. 이 어빌리티를 사용한 플레이어가 멋진 포즈를 취한다. 이 세션 장소에서 같은 포즈를 취한 사람의 수 만큼 대미지가 증가한다.(포즈를 취한 사람의 수에 사용자는 포함되지 않는다)</t>
+        </is>
+      </c>
+      <c r="G529" s="4" t="inlineStr"/>
+      <c r="H529" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I529" s="4" t="inlineStr"/>
+      <c r="J529" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>고양</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>조직:미려파</t>
+        </is>
+      </c>
+      <c r="C530" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D530" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E530" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F530" s="4" t="inlineStr">
+        <is>
+          <t>공격에 조합하여 사용한다. 공격의 대미지가 【1D6+자신의 현재 【텐션】의 10의 자리의 수】만큼 상승한다.</t>
+        </is>
+      </c>
+      <c r="G530" s="4" t="inlineStr"/>
+      <c r="H530" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I530" s="4" t="inlineStr"/>
+      <c r="J530" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>속눈썹</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>조직:미려파</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D531" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E531" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F531" s="4" t="inlineStr">
+        <is>
+          <t>원하는 캐릭터 하나를 목표로 삼는다. 지원 판정에 성공하면 목표의 관계를 하나 선택한다. 그 전투 중, 그 관계의 【심도】가 1 감소한다.</t>
+        </is>
+      </c>
+      <c r="G531" s="4" t="inlineStr"/>
+      <c r="H531" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I531" s="4" t="inlineStr"/>
+      <c r="J531" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>명품</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>조직:미려파</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D532" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E532" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F532" s="4" t="inlineStr">
+        <is>
+          <t>자신이 장비하고 있는 아이템에 다음 효과가 추가된다. 【조달판정의 주사위를 굴린 후 사용 가능. 그 조달판정에 +1의 수정을 더한다.】</t>
+        </is>
+      </c>
+      <c r="G532" s="4" t="inlineStr"/>
+      <c r="H532" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I532" s="4" t="inlineStr"/>
+      <c r="J532" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>화려함 그 자체</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>조직:미려파</t>
+        </is>
+      </c>
+      <c r="C533" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D533" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E533" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F533" s="4" t="inlineStr">
+        <is>
+          <t>자신이 주사위를 굴렸을 때 6의 주사위가 나올 때마다 자신의 【여유】가 1점 상승한다.</t>
+        </is>
+      </c>
+      <c r="G533" s="4" t="inlineStr"/>
+      <c r="H533" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I533" s="4" t="inlineStr"/>
+      <c r="J533" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>이노우에류 마녀포박술</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>조직:이노우에 가</t>
+        </is>
+      </c>
+      <c r="C534" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D534" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E534" s="3" t="inlineStr">
+        <is>
+          <t>자유</t>
+        </is>
+      </c>
+      <c r="F534" s="4" t="inlineStr">
+        <is>
+          <t>공격목표에게 1d6의 대미지를 입힌다. 목표가 마녀였을 경우, 대미지가 3 증가한다.</t>
+        </is>
+      </c>
+      <c r="G534" s="4" t="inlineStr"/>
+      <c r="H534" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I534" s="4" t="inlineStr"/>
+      <c r="J534" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>신명재판</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>조직:이노우에 가</t>
+        </is>
+      </c>
+      <c r="C535" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D535" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E535" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F535" s="4" t="inlineStr">
+        <is>
+          <t>누군가에 대한 파괴가 성공하여 【행복】이 파괴당했을 때 사용 가능. 이후, 누군가가 판정에 펌블하거나 세션이 종료될 때까지 방해판정에 플러스 2의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G535" s="4" t="inlineStr"/>
+      <c r="H535" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I535" s="4" t="inlineStr"/>
+      <c r="J535" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>이단심문 매뉴얼</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>조직:이노우에 가</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D536" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E536" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F536" s="4" t="inlineStr">
+        <is>
+          <t>【횃불】, 【고문구】를 사용한 경우 상승하는 대미지가 4점이 된다.</t>
+        </is>
+      </c>
+      <c r="G536" s="4" t="inlineStr"/>
+      <c r="H536" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I536" s="4" t="inlineStr"/>
+      <c r="J536" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>비밀의 회칙</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>조직:이노우에 가</t>
+        </is>
+      </c>
+      <c r="C537" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D537" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E537" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F537" s="4" t="inlineStr">
+        <is>
+          <t>자신이 마녀에 대해 행하는 수렵판정에 플러스 2의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G537" s="4" t="inlineStr"/>
+      <c r="H537" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I537" s="4" t="inlineStr"/>
+      <c r="J537" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>저주받은 가계</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="inlineStr">
+        <is>
+          <t>조직:이노우에 가</t>
+        </is>
+      </c>
+      <c r="C538" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D538" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E538" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F538" s="4" t="inlineStr">
+        <is>
+          <t>자신의 【텐션】이 10 이상이 된 경우, 【텐션】이 올라가는 대신 【광기】를 상승시킬 수 있게 된다. 그리고 자신이 가하는 대미지가 자신의 【광기】와 같은 수치만큼 상승한다.</t>
+        </is>
+      </c>
+      <c r="G538" s="4" t="inlineStr"/>
+      <c r="H538" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" s="4" t="inlineStr"/>
+      <c r="J538" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>마녀에게 바치는 철퇴</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>조직:이노우에 가</t>
+        </is>
+      </c>
+      <c r="C539" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D539" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E539" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F539" s="4" t="inlineStr">
+        <is>
+          <t>세션 중 마녀가 판정을 행할 때 주사위를 굴리기 전에 마이너스 1의 수정을 줄 수 있다. 이 효과는 세션 중 3회까지 사용 가능하다.</t>
+        </is>
+      </c>
+      <c r="G539" s="4" t="inlineStr"/>
+      <c r="H539" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" s="4" t="inlineStr"/>
+      <c r="J539" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>불에 굽기</t>
+        </is>
+      </c>
+      <c r="B540" s="3" t="inlineStr">
+        <is>
+          <t>무장:횃불</t>
+        </is>
+      </c>
+      <c r="C540" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D540" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E540" s="3" t="inlineStr">
+        <is>
+          <t>던지기</t>
+        </is>
+      </c>
+      <c r="F540" s="4" t="inlineStr">
+        <is>
+          <t>이 전투 중, 목표가 재기판정을 행할 때, 목표가 【불길】의 변조를 가지고 있을 경우 그 재기판정에 마이너스 1의 수정이 붙는다. 중첩되지 않음.</t>
+        </is>
+      </c>
+      <c r="G540" s="4" t="inlineStr"/>
+      <c r="H540" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 무장 어빌리티</t>
+        </is>
+      </c>
+      <c r="J540" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>화롯불</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>무장:횃불</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D541" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F541" s="4" t="inlineStr">
+        <is>
+          <t>자신이 사용하는 【화염】의 어빌리티의 코스트가 1 감소한다. (0 이하가 되지는 않는다) 그리고 자신이 사용하는 【화염】 어빌리티로 가하는 대미지가 2점 상승한다.</t>
+        </is>
+      </c>
+      <c r="G541" s="4" t="inlineStr"/>
+      <c r="H541" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" s="4" t="inlineStr"/>
+      <c r="J541" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>불길의 포위</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>무장:횃불</t>
+        </is>
+      </c>
+      <c r="C542" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D542" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E542" s="3" t="inlineStr">
+        <is>
+          <t>포획하기</t>
+        </is>
+      </c>
+      <c r="F542" s="4" t="inlineStr">
+        <is>
+          <t>이 전투 중, 목표가 【여유】를 회복할 때, 회복하는 값을 3 감소시킨다. 이 효과로 인하여 회복되는 여유가 0 미만으로는 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G542" s="4" t="inlineStr"/>
+      <c r="H542" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I542" s="4" t="inlineStr"/>
+      <c r="J542" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>계몽의 빛</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>무장:횃불</t>
+        </is>
+      </c>
+      <c r="C543" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D543" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E543" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F543" s="4" t="inlineStr">
+        <is>
+          <t>마녀에 대한 방해판정에 조합하여 사용. 이 방해에 성공한 경우 목표의 【여유】를 1D6 감소시킨다.</t>
+        </is>
+      </c>
+      <c r="G543" s="4" t="inlineStr"/>
+      <c r="H543" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I543" s="4" t="inlineStr"/>
+      <c r="J543" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>참회의 불꽃</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>무장:횃불</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D544" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E544" s="3" t="inlineStr">
+        <is>
+          <t>말하기</t>
+        </is>
+      </c>
+      <c r="F544" s="4" t="inlineStr">
+        <is>
+          <t>공격목표에게 4점의 대미지를 입힌다. 대미지 적용 후, 목표에게 【불길】의 변조를 발생시킨다.</t>
+        </is>
+      </c>
+      <c r="G544" s="4" t="inlineStr"/>
+      <c r="H544" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I544" s="4" t="inlineStr"/>
+      <c r="J544" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>마녀 추적</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>무장:횃불</t>
+        </is>
+      </c>
+      <c r="C545" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D545" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E545" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F545" s="4" t="inlineStr">
+        <is>
+          <t>수렵판정에 조합하여 사용. 수렵판정에 성공한 경우, 목표의 【지배력】의 【강도】의 감소 후, 목표의 【여유】 혹은 팔로워 하나의 【내구력】을 1D6 감소시킨다.</t>
+        </is>
+      </c>
+      <c r="G545" s="4" t="inlineStr"/>
+      <c r="H545" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I545" s="4" t="inlineStr"/>
+      <c r="J545" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>성가</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>무장:노래</t>
+        </is>
+      </c>
+      <c r="C546" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D546" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E546" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F546" s="4" t="inlineStr">
+        <is>
+          <t>공격판정에 조합하여 사용. 공격판정에 성공한 경우, 대미지가 2D6 증가한다. 만약 이 효과를 쓴 결과로 목표에게 부위 대미지를 1 이상 가한 경우 【신체부위결정표】를 사용하지 않고 대신 공격 목표가 정한 정신부위 하나와 그 상하좌우의 특기가 사용불가가 된다.</t>
+        </is>
+      </c>
+      <c r="G546" s="4" t="inlineStr"/>
+      <c r="H546" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I546" s="4" t="inlineStr"/>
+      <c r="J546" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>러브송</t>
+        </is>
+      </c>
+      <c r="B547" s="3" t="inlineStr">
+        <is>
+          <t>무장:노래</t>
+        </is>
+      </c>
+      <c r="C547" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D547" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E547" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F547" s="4" t="inlineStr">
+        <is>
+          <t>자신이 연격을 행할 때 사용가능. 그 연격에 의한 몬스터의 행동판정에 마이너스 2의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G547" s="4" t="inlineStr"/>
+      <c r="H547" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I547" s="4" t="inlineStr"/>
+      <c r="J547" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>진실의 노래</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>무장:노래</t>
+        </is>
+      </c>
+      <c r="C548" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D548" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E548" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F548" s="4" t="inlineStr">
+        <is>
+          <t>지정한 캐릭터의 재기판정에 조합하여 사용. 그 재기판정에 플러스 1의 수정이 붙는다. 이 효과는 누적되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G548" s="4" t="inlineStr"/>
+      <c r="H548" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I548" s="4" t="inlineStr"/>
+      <c r="J548" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>합창</t>
+        </is>
+      </c>
+      <c r="B549" s="3" t="inlineStr">
+        <is>
+          <t>무장:노래</t>
+        </is>
+      </c>
+      <c r="C549" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D549" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E549" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F549" s="4" t="inlineStr">
+        <is>
+          <t>자신이 연계공격으로 보조 어빌리티를 사용할 때, 그 어빌리티의 코스트를 2점 감소시킨다.(단 1 미만이 되지 않는다)</t>
+        </is>
+      </c>
+      <c r="G549" s="4" t="inlineStr"/>
+      <c r="H549" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I549" s="4" t="inlineStr"/>
+      <c r="J549" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>화답송</t>
+        </is>
+      </c>
+      <c r="B550" s="3" t="inlineStr">
+        <is>
+          <t>무장:노래</t>
+        </is>
+      </c>
+      <c r="C550" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D550" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E550" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F550" s="4" t="inlineStr">
+        <is>
+          <t>방어판정에 조합하여 사용. 방어판정에 성공한 경우, (블록의 경우 대미지 적용 후) 목표에게 1D6의 대미지를 입힌다. 만약 이 효과를 쓴 결과로 목표에게 부위 대미지를 1 이상 가한 경우 【신체부위결정표】를 사용하지 않고 대신 공격 목표가 정한 정신부위 하나와 그 상하좌우의 특기가 사용불가가 된다.</t>
+        </is>
+      </c>
+      <c r="G550" s="4" t="inlineStr"/>
+      <c r="H550" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I550" s="4" t="inlineStr"/>
+      <c r="J550" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>처형용 BGM</t>
+        </is>
+      </c>
+      <c r="B551" s="3" t="inlineStr">
+        <is>
+          <t>무장:노래</t>
+        </is>
+      </c>
+      <c r="C551" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D551" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E551" s="3" t="inlineStr">
+        <is>
+          <t>외치기</t>
+        </is>
+      </c>
+      <c r="F551" s="4" t="inlineStr">
+        <is>
+          <t>다음 자신의 행동이 종료될 때까지, 모든 캐릭터가 행하는 재기판정에 마이너스 1의 수정이 붙는다. 이 효과는 누적되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G551" s="4" t="inlineStr"/>
+      <c r="H551" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I551" s="4" t="inlineStr"/>
+      <c r="J551" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>약물강화</t>
+        </is>
+      </c>
+      <c r="B552" s="3" t="inlineStr">
+        <is>
+          <t>무장:주사기</t>
+        </is>
+      </c>
+      <c r="C552" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D552" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E552" s="3" t="inlineStr">
+        <is>
+          <t>찌르기</t>
+        </is>
+      </c>
+      <c r="F552" s="4" t="inlineStr">
+        <is>
+          <t>【흥분제】나 【진정제】를 하나 소비하여, 지원판정을 행한다. 지정특기의 판정에 성공하면 목표의 【텐션】이 3 증가하고, 그 전투 동안, 목표의 【공격력】【타격력】【방어력】【지구력】중 하나를 1점 상승시킨다. 이 효과로 증가하는 수치는 하나의 수치 당 2점까지.</t>
+        </is>
+      </c>
+      <c r="G552" s="4" t="inlineStr"/>
+      <c r="H552" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I552" s="4" t="inlineStr"/>
+      <c r="J552" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>과다투여</t>
+        </is>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>무장:주사기</t>
+        </is>
+      </c>
+      <c r="C553" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D553" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E553" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F553" s="4" t="inlineStr">
+        <is>
+          <t>누군가가 【흥분제】, 【진정제】, 【의료키트】, 【헌혈팩】을 쓴 직후에 사용 가능. 해당 아이템을 사용한 캐릭터 한 명을 목표로 정한다. 자신이 【흥분제】나 【진정제】를 하나 소비하면 목표가 사용한 아이템의 효과를 없애고, 목표에게 2D6의 대미지를 가할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G553" s="4" t="inlineStr"/>
+      <c r="H553" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I553" s="4" t="inlineStr"/>
+      <c r="J553" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>독살</t>
+        </is>
+      </c>
+      <c r="B554" s="3" t="inlineStr">
+        <is>
+          <t>무장:주사기</t>
+        </is>
+      </c>
+      <c r="C554" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D554" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E554" s="3" t="inlineStr">
+        <is>
+          <t>쏘기</t>
+        </is>
+      </c>
+      <c r="F554" s="4" t="inlineStr">
+        <is>
+          <t>명중판정에 성공한 경우, 1D6을 굴린다. 나온 눈이 1~5일 경우, 공격목표에게 그 눈과 같은 만큼의 대미지를 입힌다. 나온 눈이 6일 경우, 공격목표에게 부위 대미지를 하나 입힌다.(목표가 팔로워일 경우, 무력화)부위 대미지에 대해 방어를 시도할 수 없다. 부위 대미지의 부위는 신체부위결정표로 정한다.</t>
+        </is>
+      </c>
+      <c r="G554" s="4" t="inlineStr"/>
+      <c r="H554" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I554" s="4" t="inlineStr"/>
+      <c r="J554" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>미약</t>
+        </is>
+      </c>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>무장:주사기</t>
+        </is>
+      </c>
+      <c r="C555" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D555" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E555" s="3" t="inlineStr">
+        <is>
+          <t>속이기</t>
+        </is>
+      </c>
+      <c r="F555" s="4" t="inlineStr">
+        <is>
+          <t>【흥분제】나 【진정제】를 하나 소비하여, 지원판정을 행한다. 지정특기의 판정에 성공하면 목표의 【심도】가 1 이상이 된 관계를 하나 정한다. 그 【심도】를 1 증가시킨다.</t>
+        </is>
+      </c>
+      <c r="G555" s="4" t="inlineStr"/>
+      <c r="H555" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I555" s="4" t="inlineStr"/>
+      <c r="J555" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>마약</t>
+        </is>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>무장:주사기</t>
+        </is>
+      </c>
+      <c r="C556" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D556" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E556" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F556" s="4" t="inlineStr">
+        <is>
+          <t>공격판정에 조합하여 사용. 공격판정에 성공한 경우, 대미지 적용 후, 목표는 어빌리티 사용자가 고르는 변조 하나를 받는다.</t>
+        </is>
+      </c>
+      <c r="G556" s="4" t="inlineStr"/>
+      <c r="H556" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I556" s="4" t="inlineStr"/>
+      <c r="J556" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>진실의 혈청</t>
+        </is>
+      </c>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>무장:주사기</t>
+        </is>
+      </c>
+      <c r="C557" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D557" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E557" s="3" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="F557" s="4" t="inlineStr">
+        <is>
+          <t>지원판정은 랜덤으로 결정된 지정특기로 행한다. 이 지원판정은 목표가 자신에게 가진 관계의 【심도】가 플러스 수정으로 붙는다. 목표의 약점이 밝혀진다.</t>
+        </is>
+      </c>
+      <c r="G557" s="4" t="inlineStr"/>
+      <c r="H557" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" s="4" t="inlineStr"/>
+      <c r="J557" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>거짓 정보</t>
+        </is>
+      </c>
+      <c r="B558" s="3" t="inlineStr">
+        <is>
+          <t>무장:소문</t>
+        </is>
+      </c>
+      <c r="C558" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D558" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E558" s="3" t="inlineStr">
+        <is>
+          <t>말하기</t>
+        </is>
+      </c>
+      <c r="F558" s="4" t="inlineStr">
+        <is>
+          <t>공격이 성공한 경우, 공격목표에게 1점의 대미지를 가한다. 대미지 적용 후, 목표에게 【불길】과 【방해】의 변조가 발동된다.</t>
+        </is>
+      </c>
+      <c r="G558" s="4" t="inlineStr"/>
+      <c r="H558" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I558" s="4" t="inlineStr"/>
+      <c r="J558" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>나쁜 소문</t>
+        </is>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>무장:소문</t>
+        </is>
+      </c>
+      <c r="C559" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D559" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E559" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F559" s="4" t="inlineStr">
+        <is>
+          <t>방해판정에 조합하여 사용. 이 방해에 성공한 경우, 목표의 팔로워 하나의 【내구력】을 1D6 감소시킨다. 흡혈귀나 마녀의 경우, PC가 방해에 실패했을 경우 사용가능. 방해에 실패한 PC 한 명을 목표로 정한다. 목표의 【여유】를 1D6 감소시킨다. 0 미만이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G559" s="4" t="inlineStr"/>
+      <c r="H559" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I559" s="4" t="inlineStr"/>
+      <c r="J559" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>낚시</t>
+        </is>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>무장:소문</t>
+        </is>
+      </c>
+      <c r="C560" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D560" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E560" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F560" s="4" t="inlineStr">
+        <is>
+          <t>자신이 연격을 행할 때 사용가능. 연격에 의한 몬스터의 행동판정이 실패하거나, 자신의 연격판정이 성공한 경우, 목표의 【여유】를 2D6 감소시킬 수 있다. 흡혈귀나 마녀의 경우, 자신이 파괴나 습격, 접촉을 할 때 사용 가능. 파괴, 습격, 접촉의 목표 이외의 PC 1명 을 목표로 선택. 그 파괴나 습격, 접촉에 대해 목표 이외에는 방해를 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G560" s="4" t="inlineStr"/>
+      <c r="H560" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I560" s="4" t="inlineStr"/>
+      <c r="J560" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>안내인</t>
+        </is>
+      </c>
+      <c r="B561" s="3" t="inlineStr">
+        <is>
+          <t>무장:소문</t>
+        </is>
+      </c>
+      <c r="C561" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D561" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E561" s="3" t="inlineStr">
+        <is>
+          <t>퇴로</t>
+        </is>
+      </c>
+      <c r="F561" s="4" t="inlineStr">
+        <is>
+          <t>목표는 아이템을 하나 정하여 입수한다. 지원판정이 스페셜로 성공했을 경우, 목표는 통상 아이템 대신 자신이 소속된 조직의 레어 아이템을 하나 습득해도 좋다. 흡혈귀나 마녀가 지원판정에 스페셜로 성공할 경우, 통상 아이템 대신 아무 조직의 레어아이템을 하나 입수해도 좋다.</t>
+        </is>
+      </c>
+      <c r="G561" s="4" t="inlineStr"/>
+      <c r="H561" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I561" s="4" t="inlineStr"/>
+      <c r="J561" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>주의보</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="inlineStr">
+        <is>
+          <t>무장:소문</t>
+        </is>
+      </c>
+      <c r="C562" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D562" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E562" s="3" t="inlineStr">
+        <is>
+          <t>인맥</t>
+        </is>
+      </c>
+      <c r="F562" s="4" t="inlineStr">
+        <is>
+          <t>이 어빌리티는 결전페이즈에 사용 불가. 메인페이즈에서 헌터의 행동을 행하는 대신 사용 가능. 지원 판정에 성공하면, 목표가 행하는 파괴판정, 습격판정, 학살판정, 접촉판정에 마이너스 1의 수정이 붙는다(최대 마이너스 2). 흡혈귀나 마녀의 경우, 몬스터의 행동 대신 사용가능. 지원판정에 성공하면 목표가 행하는 수렵판정, 전초전판정에 마이너스 1의 수정이 붙는다(최대 마이너스 2).</t>
+        </is>
+      </c>
+      <c r="G562" s="4" t="inlineStr"/>
+      <c r="H562" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I562" s="4" t="inlineStr"/>
+      <c r="J562" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>도시전설</t>
+        </is>
+      </c>
+      <c r="B563" s="3" t="inlineStr">
+        <is>
+          <t>무장:소문</t>
+        </is>
+      </c>
+      <c r="C563" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D563" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E563" s="3" t="inlineStr">
+        <is>
+          <t>보기</t>
+        </is>
+      </c>
+      <c r="F563" s="4" t="inlineStr">
+        <is>
+          <t>메인페이즈에 자신이 파괴, 습격, 학살, 접촉의 목표가 되었을 때, 그 처리가 끝나고 사용가능. 지정특기의 판정에 성공하면 목표의 부위 중 하나를 고른다. GM은 목표의 【약점】이 그 부위였을 경우, 이를 플레이어에게 알릴 것.</t>
+        </is>
+      </c>
+      <c r="G563" s="4" t="inlineStr"/>
+      <c r="H563" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I563" s="4" t="inlineStr"/>
+      <c r="J563" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>스페인 거미</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>무장:고문도구</t>
+        </is>
+      </c>
+      <c r="C564" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D564" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E564" s="3" t="inlineStr">
+        <is>
+          <t>던지기</t>
+        </is>
+      </c>
+      <c r="F564" s="4" t="inlineStr">
+        <is>
+          <t>지원판정에 성공하면 목표는 【포박】의 변조를 받는다. 그리고 목표가 이미 【포박】을 받고 있다면 【공황】, 【포박】과 【공황】을 함께 받고 있다면 목표에게 2d6의 대미지를 가한다. 이 효과로 인해 부위 대미지를 입어도, 재기판정은 일어나지 않는다.</t>
+        </is>
+      </c>
+      <c r="G564" s="4" t="inlineStr"/>
+      <c r="H564" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I564" s="4" t="inlineStr"/>
+      <c r="J564" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>악어의 가위</t>
+        </is>
+      </c>
+      <c r="B565" s="3" t="inlineStr">
+        <is>
+          <t>무장:고문도구</t>
+        </is>
+      </c>
+      <c r="C565" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D565" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E565" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F565" s="4" t="inlineStr">
+        <is>
+          <t>팔로워를 목표로 한 전초전, 혹은 PC를 목표로 한 접촉에 조합하여 사용. 이 판정에 성공하면, 그 세션 중 2번까지, 캐릭터를 하나 골라 그 캐릭터의 수렵, 전초전, 휴식, 파괴, 습격, 휴양, 접촉의 판정에 플러스 2나 마이너스 2의 수정을 붙일 수 있다.</t>
+        </is>
+      </c>
+      <c r="G565" s="4" t="inlineStr"/>
+      <c r="H565" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I565" s="4" t="inlineStr"/>
+      <c r="J565" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>테슬라 부인</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>무장:고문도구</t>
+        </is>
+      </c>
+      <c r="C566" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D566" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E566" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F566" s="4" t="inlineStr">
+        <is>
+          <t>공격에 조합하여 사용. 공격판정에 성공시, 공격목표는 【공황】의 변조를 받고, 공격목표는 라운드 종료시까지 자신이 행하는 판정들 에 마이너스 2의 수정이 붙는다.</t>
+        </is>
+      </c>
+      <c r="G566" s="4" t="inlineStr"/>
+      <c r="H566" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I566" s="4" t="inlineStr"/>
+      <c r="J566" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>잔소리꾼의 재갈</t>
+        </is>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>무장:고문도구</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D567" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E567" s="3" t="inlineStr">
+        <is>
+          <t>조이기</t>
+        </is>
+      </c>
+      <c r="F567" s="4" t="inlineStr">
+        <is>
+          <t>지원판정에 성공하면, 목표가 접촉이나 지원을 할 때마다, 그 처리를 하기 전에 목표에게 2d6의 대미지를 가한다.</t>
+        </is>
+      </c>
+      <c r="G567" s="4" t="inlineStr"/>
+      <c r="H567" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I567" s="4" t="inlineStr"/>
+      <c r="J567" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>죽음의 진자</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>무장:고문도구</t>
+        </is>
+      </c>
+      <c r="C568" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D568" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E568" s="3" t="inlineStr">
+        <is>
+          <t>위협하기</t>
+        </is>
+      </c>
+      <c r="F568" s="4" t="inlineStr">
+        <is>
+          <t>지원판정에 성공하면, 라운드 종료시에 1d6을 굴린다. 그 눈이 어빌리티를 사용했을 때부터 경과한 라운드 수 이상이면 목표에게 【공황】의 변조를 발동시킨다. 그 눈이 경과한 라운드 수 미만이면 목표에게 4D6의 대미지를 입힌다. 이 어빌리티를 한번 사용하면 이 어빌리티의 효과에 의해 4d6의 대미지를 입힐 때 까지 다시 이 어빌리티를 쓸 수 없다.</t>
+        </is>
+      </c>
+      <c r="G568" s="4" t="inlineStr"/>
+      <c r="H568" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I568" s="4" t="inlineStr"/>
+      <c r="J568" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>아이언 메이든</t>
+        </is>
+      </c>
+      <c r="B569" s="3" t="inlineStr">
+        <is>
+          <t>무장:고문도구</t>
+        </is>
+      </c>
+      <c r="C569" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D569" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E569" s="3" t="inlineStr">
+        <is>
+          <t>설치하기</t>
+        </is>
+      </c>
+      <c r="F569" s="4" t="inlineStr">
+        <is>
+          <t>공격목표에게 1d6의 대미지를 입힌다. 대미지 적용 후, 공격목표는 【공황】【포박】의 변조가 발동된다. 목표가 【공황】【포박】의 변조가 이미 있다면, 목표는 이 공격에 대해 회피를 할 수 없고, 대미지 적용 후 【유혈】【중상】의 변조가 발동된다. 이 효과에 의해 부위 대미지 가 발생해도, 재기판정은 일어나지 않는다.</t>
+        </is>
+      </c>
+      <c r="G569" s="4" t="inlineStr"/>
+      <c r="H569" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I569" s="4" t="inlineStr"/>
+      <c r="J569" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>매력강화</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>무장:화장품</t>
+        </is>
+      </c>
+      <c r="C570" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D570" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E570" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F570" s="4" t="inlineStr">
+        <is>
+          <t>메인페이즈 행동에 조합하여 사용. 판정에 성공시, 씬에 등장한 캐릭터 중 하나는 아이템 【매력강화】를 획득한다. 이 아이템은 양도가 불가능하며, 세션 종료시에 소멸된다. 【매력강화】를 가진 캐릭터는 교류, 휴식, 휴양, 접촉의 각 판정에 플러스 2가 붙는다. 이 효과는 누적되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G570" s="4" t="inlineStr"/>
+      <c r="H570" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I570" s="4" t="inlineStr"/>
+      <c r="J570" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>전투화장</t>
+        </is>
+      </c>
+      <c r="B571" s="3" t="inlineStr">
+        <is>
+          <t>무장:화장품</t>
+        </is>
+      </c>
+      <c r="C571" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D571" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E571" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F571" s="4" t="inlineStr">
+        <is>
+          <t>메인페이즈 행동에 조합하여 사용. 판정에 성공시, 씬에 등장한 캐릭터 중 하나는 아이템 【전투화장】을 획득한다. 이 아이템은 양도가 불가능하며, 세션 종료시에 소멸된다. 【매력강화】를 가진 캐릭터는 수렵, 전초전, 파괴, 습격의 각 판정에 플러스 2가 붙는다. 이 효과는 누적되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G571" s="4" t="inlineStr"/>
+      <c r="H571" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I571" s="4" t="inlineStr"/>
+      <c r="J571" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>변장</t>
+        </is>
+      </c>
+      <c r="B572" s="3" t="inlineStr">
+        <is>
+          <t>무장:화장품</t>
+        </is>
+      </c>
+      <c r="C572" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D572" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E572" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F572" s="4" t="inlineStr">
+        <is>
+          <t>전투중, 자신이 행하는 최초의 공격판정에 조합하여 사용. 공격판정에 성공하면, 공격목표는 그 공격을 방어할 수 없고, 【공황】의 변조 가 발동된다. 그리고 공격의 대미지는 2d6 증가한다.</t>
+        </is>
+      </c>
+      <c r="G572" s="4" t="inlineStr"/>
+      <c r="H572" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I572" s="4" t="inlineStr"/>
+      <c r="J572" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>쉐이딩</t>
+        </is>
+      </c>
+      <c r="B573" s="3" t="inlineStr">
+        <is>
+          <t>무장:화장품</t>
+        </is>
+      </c>
+      <c r="C573" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D573" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E573" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F573" s="4" t="inlineStr">
+        <is>
+          <t>자신 이외의 캐릭터가 블록판정이나 회피판정을 할 때, 그 코스트를 내 텐션에서 대신 낼 수 있다.</t>
+        </is>
+      </c>
+      <c r="G573" s="4" t="inlineStr"/>
+      <c r="H573" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I573" s="4" t="inlineStr"/>
+      <c r="J573" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>고속 메이크업</t>
+        </is>
+      </c>
+      <c r="B574" s="3" t="inlineStr">
+        <is>
+          <t>무장:화장품</t>
+        </is>
+      </c>
+      <c r="C574" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D574" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E574" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F574" s="4" t="inlineStr">
+        <is>
+          <t>【매력강화】【전투화장】의 효과가 같은 씬에 있는 아군 캐릭터 전원이 된다. 그리고 【전투화장】【매력강화】의 대상이 된 캐릭터의 【텐션】을 2 증가시킬 수 있다. 하지 않아도 좋다.</t>
+        </is>
+      </c>
+      <c r="G574" s="4" t="inlineStr"/>
+      <c r="H574" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I574" s="4" t="inlineStr"/>
+      <c r="J574" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>변신마법</t>
+        </is>
+      </c>
+      <c r="B575" s="3" t="inlineStr">
+        <is>
+          <t>무장:화장품</t>
+        </is>
+      </c>
+      <c r="C575" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D575" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E575" s="3" t="inlineStr">
+        <is>
+          <t>나타나기</t>
+        </is>
+      </c>
+      <c r="F575" s="4" t="inlineStr">
+        <is>
+          <t>전투에서 한번만 사용할 수 있다. 지원판정에 성공하면 자신의 【여유】가 【【내구력】+자신의 【레벨】】이 되고, 전투 종료시까지 자신이 가하는 대미지가 자신의 【레벨】만큼 증가한다. 그리고 추가행동을 1회 획득한다.</t>
+        </is>
+      </c>
+      <c r="G575" s="4" t="inlineStr"/>
+      <c r="H575" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I575" s="4" t="inlineStr"/>
+      <c r="J575" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>포 뜨기</t>
+        </is>
+      </c>
+      <c r="B576" s="3" t="inlineStr">
+        <is>
+          <t>무장:요리</t>
+        </is>
+      </c>
+      <c r="C576" s="3" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="D576" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E576" s="3" t="inlineStr">
+        <is>
+          <t>베기</t>
+        </is>
+      </c>
+      <c r="F576" s="4" t="inlineStr">
+        <is>
+          <t>이 공격에 성공하면 공격목표에게 1D6-1의 대미지를 입힌다. 이 공격으로 목표에게 부위 대미지를 1점 이상 줬을 때, 목표는 【내구력】 이 1 감소한다.</t>
+        </is>
+      </c>
+      <c r="G576" s="4" t="inlineStr"/>
+      <c r="H576" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I576" s="4" t="inlineStr"/>
+      <c r="J576" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>고기 굽기</t>
+        </is>
+      </c>
+      <c r="B577" s="3" t="inlineStr">
+        <is>
+          <t>무장:요리</t>
+        </is>
+      </c>
+      <c r="C577" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D577" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E577" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F577" s="4" t="inlineStr">
+        <is>
+          <t>선제판정에 조합하여 사용. 선제판정에 성공시, 목표는 【불길】의 변조를 받는다. 몬스터의 경우, 행동 순서 결정시에 목표 하나를 고른다. 목표가 선제판정에 실패하면 목표는 【불길】의 변조를 받는다.</t>
+        </is>
+      </c>
+      <c r="G577" s="4" t="inlineStr"/>
+      <c r="H577" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I577" s="4" t="inlineStr"/>
+      <c r="J577" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>소금 뿌리기</t>
+        </is>
+      </c>
+      <c r="B578" s="3" t="inlineStr">
+        <is>
+          <t>무장:요리</t>
+        </is>
+      </c>
+      <c r="C578" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D578" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E578" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F578" s="4" t="inlineStr">
+        <is>
+          <t>누군가가 대미지를 입으면 원하는 만큼 자신의 【텐션】을 증가시킬 수 있다(최대 5점). 증가한 텐션 수치만큼 그 대미지를 증가시킨다. 이 효과는 1라운드에 1회만 사용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G578" s="4" t="inlineStr"/>
+      <c r="H578" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I578" s="4" t="inlineStr"/>
+      <c r="J578" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>간 보기</t>
+        </is>
+      </c>
+      <c r="B579" s="3" t="inlineStr">
+        <is>
+          <t>무장:요리</t>
+        </is>
+      </c>
+      <c r="C579" s="3" t="inlineStr">
+        <is>
+          <t>상주</t>
+        </is>
+      </c>
+      <c r="D579" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E579" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F579" s="4" t="inlineStr">
+        <is>
+          <t>결전페이즈의 지원판정으로 휴식(몬스터의 경우에는 휴양)을 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G579" s="4" t="inlineStr"/>
+      <c r="H579" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I579" s="4" t="inlineStr"/>
+      <c r="J579" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>오늘의 접시</t>
+        </is>
+      </c>
+      <c r="B580" s="3" t="inlineStr">
+        <is>
+          <t>무장:요리</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="inlineStr">
+        <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="D580" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E580" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F580" s="4" t="inlineStr">
+        <is>
+          <t>휴식판정이나 휴양판정에 조합하여 사용. 판정 성공시, 그 씬에 등장한 캐릭터 중 넷까지 목표를 골라 여유를 1D6 증가시킨다.</t>
+        </is>
+      </c>
+      <c r="G580" s="4" t="inlineStr"/>
+      <c r="H580" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I580" s="4" t="inlineStr"/>
+      <c r="J580" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>향신료</t>
+        </is>
+      </c>
+      <c r="B581" s="3" t="inlineStr">
+        <is>
+          <t>무장:요리</t>
+        </is>
+      </c>
+      <c r="C581" s="3" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D581" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E581" s="3" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+      <c r="F581" s="4" t="inlineStr">
+        <is>
+          <t>캐릭터 하나를 목표로 정한다. 지정특기의 판정에 성공하면 전투종료시까지 목표의 특성치 중 하나를 골라 1점 증가시킨다. 이 효과 는 같은 목표에 대해 같은 특성치를 2점 이상 증가시킬 수 없다.</t>
+        </is>
+      </c>
+      <c r="G581" s="4" t="inlineStr"/>
+      <c r="H581" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I581" s="4" t="inlineStr"/>
+      <c r="J581" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I509"/>
+  <autoFilter ref="A1:J581"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21982,7 +27566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -21991,6 +27575,7 @@
     <col width="48.2" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="26.6" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22024,6 +27609,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>룰북</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -22051,6 +27641,11 @@
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -22078,6 +27673,11 @@
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -22105,6 +27705,11 @@
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -22132,6 +27737,11 @@
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -22159,6 +27769,11 @@
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -22186,6 +27801,11 @@
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -22213,6 +27833,11 @@
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -22240,6 +27865,11 @@
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -22267,6 +27897,11 @@
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -22294,6 +27929,11 @@
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -22321,6 +27961,11 @@
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -22348,6 +27993,11 @@
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -22375,6 +28025,11 @@
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -22402,6 +28057,11 @@
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -22429,6 +28089,11 @@
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -22456,6 +28121,11 @@
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -22483,6 +28153,11 @@
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -22510,6 +28185,11 @@
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -22537,6 +28217,11 @@
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -22563,6 +28248,11 @@
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -22589,6 +28279,11 @@
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -22615,6 +28310,11 @@
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -22641,6 +28341,11 @@
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -22667,6 +28372,11 @@
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -22693,6 +28403,11 @@
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -22719,6 +28434,11 @@
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -22745,6 +28465,11 @@
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -22771,6 +28496,11 @@
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -22797,6 +28527,11 @@
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -22823,6 +28558,11 @@
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -22850,6 +28590,11 @@
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -22877,6 +28622,11 @@
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -22904,6 +28654,11 @@
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -22931,6 +28686,11 @@
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -22958,6 +28718,11 @@
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -22985,6 +28750,11 @@
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -23011,6 +28781,11 @@
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -23037,6 +28812,11 @@
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -23063,6 +28843,11 @@
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -23089,6 +28874,11 @@
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -23115,6 +28905,11 @@
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -23141,6 +28936,11 @@
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -23167,6 +28967,11 @@
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -23193,6 +28998,11 @@
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -23223,6 +29033,11 @@
           <t>역) 2017년 9월 1일 추가 에라타 반영. 기존(誤) : 무작위로 변조 4개 발동</t>
         </is>
       </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -23249,9 +29064,138 @@
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>기본룰북</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>학생수첩</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>사립 심연 여학원 소속의 레어아이템. 자신이 판정의 주사위를 굴리기 직전에 사용 가능. 판정에서 굴린 주사위의 눈이 10 이상인 경우 스페셜이 발생한다.</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 레어 아이템</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>키친 카</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>생츄어리 소속의 레어아이템. 자신이 휴식을 행할 때 사용 가능. 휴식에 성공하면 그 씬에 등장하고 있는 다른 헌터의 [여유]가 [내구력]과 같은 만큼 상승한다.</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 레어 아이템</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>마녀의 유물</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>미려파 소속의 레어아이템. 자신이 방해를 행할 때 사용 가능. 그 방해의 코스트가 0이 된다.</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 레어 아이템</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>성변의 종</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>이노우에 가 소속의 레어아이템. 자신이 상주 이외의 어빌리티를 사용할 때 사용 가능. 그 어빌리티 하나의 코스트를 0으로 한다.</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>※ 서플리먼트 길티 위치즈 수록 레어 아이템</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>길티 위치즈</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:G51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>